--- a/locations.xlsx
+++ b/locations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0e1a8f0ccba4ae8f/Boardgames/Spyfall/webapp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F1719E0-FC54-4510-A14B-7DDBC994B3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{7F1719E0-FC54-4510-A14B-7DDBC994B3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{687E9C01-A992-443D-B19E-DAA1EF690DAF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{ECB1663B-1660-49C2-BB3F-310FC64B3460}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{ECB1663B-1660-49C2-BB3F-310FC64B3460}"/>
   </bookViews>
   <sheets>
     <sheet name="Location A" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Role A1</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Role B3</t>
+  </si>
+  <si>
+    <t>Role</t>
   </si>
 </sst>
 </file>
@@ -429,21 +432,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C30512-2CBD-43D7-B2C6-490239A5FF95}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -454,21 +462,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9841D522-56C4-4367-88B5-1E44452857C1}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>

--- a/locations.xlsx
+++ b/locations.xlsx
@@ -8,13 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0e1a8f0ccba4ae8f/Boardgames/Spyfall/webapp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{7F1719E0-FC54-4510-A14B-7DDBC994B3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{687E9C01-A992-443D-B19E-DAA1EF690DAF}"/>
+  <xr:revisionPtr revIDLastSave="432" documentId="8_{7F1719E0-FC54-4510-A14B-7DDBC994B3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F3C092B-18E2-4DF2-A2F6-92050332D03F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{ECB1663B-1660-49C2-BB3F-310FC64B3460}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="11" xr2:uid="{ECB1663B-1660-49C2-BB3F-310FC64B3460}"/>
   </bookViews>
   <sheets>
-    <sheet name="Location A" sheetId="1" r:id="rId1"/>
-    <sheet name="Location B" sheetId="2" r:id="rId2"/>
+    <sheet name="Feudal Japan" sheetId="1" r:id="rId1"/>
+    <sheet name="Submarine" sheetId="2" r:id="rId2"/>
+    <sheet name="Small Claims Court" sheetId="3" r:id="rId3"/>
+    <sheet name="Circus" sheetId="4" r:id="rId4"/>
+    <sheet name="Tropical Island" sheetId="5" r:id="rId5"/>
+    <sheet name="Starship Enterprise" sheetId="6" r:id="rId6"/>
+    <sheet name="Broadway Theater" sheetId="7" r:id="rId7"/>
+    <sheet name="Ancient Greece" sheetId="8" r:id="rId8"/>
+    <sheet name="Operating Room" sheetId="9" r:id="rId9"/>
+    <sheet name="Cemetery" sheetId="10" r:id="rId10"/>
+    <sheet name="1920s Speakeasy" sheetId="11" r:id="rId11"/>
+    <sheet name="Wild West Saloon" sheetId="12" r:id="rId12"/>
+    <sheet name="Elite University" sheetId="13" r:id="rId13"/>
+    <sheet name="Zoo" sheetId="14" r:id="rId14"/>
+    <sheet name="Commercial Airplane" sheetId="15" r:id="rId15"/>
+    <sheet name="Fancy Restaurant" sheetId="16" r:id="rId16"/>
+    <sheet name="Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Supermarket" sheetId="18" r:id="rId18"/>
+    <sheet name="Ski Resort" sheetId="20" r:id="rId19"/>
+    <sheet name="National Park" sheetId="19" r:id="rId20"/>
+    <sheet name="Pirate Ship" sheetId="21" r:id="rId21"/>
+    <sheet name="Ancient Egypt" sheetId="22" r:id="rId22"/>
+    <sheet name="Prehistoric Cave" sheetId="23" r:id="rId23"/>
+    <sheet name="Underwater City" sheetId="24" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,40 +62,562 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
-  <si>
-    <t>Role A1</t>
-  </si>
-  <si>
-    <t>Role A2</t>
-  </si>
-  <si>
-    <t>Role A3</t>
-  </si>
-  <si>
-    <t>Role B1</t>
-  </si>
-  <si>
-    <t>Role B2</t>
-  </si>
-  <si>
-    <t>Role B3</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="179">
   <si>
     <t>Role</t>
+  </si>
+  <si>
+    <t>Performer</t>
+  </si>
+  <si>
+    <t>Police Officer</t>
+  </si>
+  <si>
+    <t>Captain</t>
+  </si>
+  <si>
+    <t>Sailor</t>
+  </si>
+  <si>
+    <t>Sonar Technician</t>
+  </si>
+  <si>
+    <t>Navigator</t>
+  </si>
+  <si>
+    <t>Engineer</t>
+  </si>
+  <si>
+    <t>Stow Away</t>
+  </si>
+  <si>
+    <t>Marine Biologist</t>
+  </si>
+  <si>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>Judge</t>
+  </si>
+  <si>
+    <t>Lawyer</t>
+  </si>
+  <si>
+    <t>Lion Tamer</t>
+  </si>
+  <si>
+    <t>Clown</t>
+  </si>
+  <si>
+    <t>Trapeze Artist</t>
+  </si>
+  <si>
+    <t>Ringmaster</t>
+  </si>
+  <si>
+    <t>Lost Child</t>
+  </si>
+  <si>
+    <t>Popcorn Vendor</t>
+  </si>
+  <si>
+    <t>Elephant Poo Cleaner</t>
+  </si>
+  <si>
+    <t>Contortionist</t>
+  </si>
+  <si>
+    <t>Surfer</t>
+  </si>
+  <si>
+    <t>Castaway</t>
+  </si>
+  <si>
+    <t>Cannibal</t>
+  </si>
+  <si>
+    <t>Pirate</t>
+  </si>
+  <si>
+    <t>Tourist</t>
+  </si>
+  <si>
+    <t>Hula Dancer</t>
+  </si>
+  <si>
+    <t>Scientist</t>
+  </si>
+  <si>
+    <t>Kirk</t>
+  </si>
+  <si>
+    <t>Spock</t>
+  </si>
+  <si>
+    <t>Uhura</t>
+  </si>
+  <si>
+    <t>Scotty</t>
+  </si>
+  <si>
+    <t>A Klingon Invader</t>
+  </si>
+  <si>
+    <t>A Tribbles Dealer</t>
+  </si>
+  <si>
+    <t>McCoy, the cranky Doctor</t>
+  </si>
+  <si>
+    <t>Passenger</t>
+  </si>
+  <si>
+    <t>Terrorist</t>
+  </si>
+  <si>
+    <t>Nurse</t>
+  </si>
+  <si>
+    <t>Bar Tender</t>
+  </si>
+  <si>
+    <t>Security Guard</t>
+  </si>
+  <si>
+    <t>Gun Slinger</t>
+  </si>
+  <si>
+    <t>Prostitute</t>
+  </si>
+  <si>
+    <t>Piano Player</t>
+  </si>
+  <si>
+    <t>Sheriff</t>
+  </si>
+  <si>
+    <t>Poker Player</t>
+  </si>
+  <si>
+    <t>Railroad Tycoon</t>
+  </si>
+  <si>
+    <t>Freshman Student</t>
+  </si>
+  <si>
+    <t>University Police</t>
+  </si>
+  <si>
+    <t>Graduate Student</t>
+  </si>
+  <si>
+    <t>Dean</t>
+  </si>
+  <si>
+    <t>Veterinarian</t>
+  </si>
+  <si>
+    <t>Ticket Agent</t>
+  </si>
+  <si>
+    <t>Cleaning Staff</t>
+  </si>
+  <si>
+    <t>Lion Feeder</t>
+  </si>
+  <si>
+    <t>Tour Guide</t>
+  </si>
+  <si>
+    <t>Reptile Specialist</t>
+  </si>
+  <si>
+    <t>Food Vendor</t>
+  </si>
+  <si>
+    <t>Businessperson</t>
+  </si>
+  <si>
+    <t>Flight Attendant</t>
+  </si>
+  <si>
+    <t>Air Marshall</t>
+  </si>
+  <si>
+    <t>First Class Passenger</t>
+  </si>
+  <si>
+    <t>Economy Class Passenger</t>
+  </si>
+  <si>
+    <t>Maître d'</t>
+  </si>
+  <si>
+    <t>Master Chef</t>
+  </si>
+  <si>
+    <t>Waiter</t>
+  </si>
+  <si>
+    <t>Sommelier</t>
+  </si>
+  <si>
+    <t>Food Critic</t>
+  </si>
+  <si>
+    <t>Diner on a date</t>
+  </si>
+  <si>
+    <t>Mixologist</t>
+  </si>
+  <si>
+    <t>Violinist</t>
+  </si>
+  <si>
+    <t>Bank Teller</t>
+  </si>
+  <si>
+    <t>Armored Car Driver</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Bank Robber</t>
+  </si>
+  <si>
+    <t>Financial Consultant</t>
+  </si>
+  <si>
+    <t>Lottery Winner</t>
+  </si>
+  <si>
+    <t>Shopper</t>
+  </si>
+  <si>
+    <t>Cashier</t>
+  </si>
+  <si>
+    <t>Shopping Cart Attendant</t>
+  </si>
+  <si>
+    <t>Deli Chef</t>
+  </si>
+  <si>
+    <t>Food Sample Attendant</t>
+  </si>
+  <si>
+    <t>Butcher</t>
+  </si>
+  <si>
+    <t>Shelf Stocker</t>
+  </si>
+  <si>
+    <t>Grocery Bagger</t>
+  </si>
+  <si>
+    <t>Celebrity</t>
+  </si>
+  <si>
+    <t>Ski Lift Operator</t>
+  </si>
+  <si>
+    <t>Ski Instructor</t>
+  </si>
+  <si>
+    <t>Medic</t>
+  </si>
+  <si>
+    <t>Ski Boot Fitter</t>
+  </si>
+  <si>
+    <t>Olympic Skier</t>
+  </si>
+  <si>
+    <t>Showoff</t>
+  </si>
+  <si>
+    <t>Park Ranger</t>
+  </si>
+  <si>
+    <t>Backpacker</t>
+  </si>
+  <si>
+    <t>Ecologist</t>
+  </si>
+  <si>
+    <t>Rock Climber</t>
+  </si>
+  <si>
+    <t>Poacher</t>
+  </si>
+  <si>
+    <t>Biologist</t>
+  </si>
+  <si>
+    <t>Gift Shop Owner</t>
+  </si>
+  <si>
+    <t>Swashbuckler</t>
+  </si>
+  <si>
+    <t>Cabin Boy</t>
+  </si>
+  <si>
+    <t>Treasure Hunter</t>
+  </si>
+  <si>
+    <t>Lookout</t>
+  </si>
+  <si>
+    <t>Canoneer</t>
+  </si>
+  <si>
+    <t>Pharaoh</t>
+  </si>
+  <si>
+    <t>Priest</t>
+  </si>
+  <si>
+    <t>Merchant</t>
+  </si>
+  <si>
+    <t>Imbalmer</t>
+  </si>
+  <si>
+    <t>Cleopatra</t>
+  </si>
+  <si>
+    <t>Chariot Salesperson</t>
+  </si>
+  <si>
+    <t>Roman</t>
+  </si>
+  <si>
+    <t>Eunuch</t>
+  </si>
+  <si>
+    <t>Caveman Hunter</t>
+  </si>
+  <si>
+    <t>Caveman Gatherer</t>
+  </si>
+  <si>
+    <t>Shaman</t>
+  </si>
+  <si>
+    <t>Wheel Carver</t>
+  </si>
+  <si>
+    <t>Cave Artist</t>
+  </si>
+  <si>
+    <t>Mammoth Rider</t>
+  </si>
+  <si>
+    <t>Tanner</t>
+  </si>
+  <si>
+    <t>Mermaid</t>
+  </si>
+  <si>
+    <t>Deep Sea Diver</t>
+  </si>
+  <si>
+    <t>Seaweed Farmer</t>
+  </si>
+  <si>
+    <t>Poseidon</t>
+  </si>
+  <si>
+    <t>Trident Merchant</t>
+  </si>
+  <si>
+    <t>Jelly Fish Herder</t>
+  </si>
+  <si>
+    <t>Sponge Dealer</t>
+  </si>
+  <si>
+    <t>Anemone Comber</t>
+  </si>
+  <si>
+    <t>Pirate Captain</t>
+  </si>
+  <si>
+    <t>Royal Navy Prisoner</t>
+  </si>
+  <si>
+    <t>Sailor on the Plank</t>
+  </si>
+  <si>
+    <t>Peasant</t>
+  </si>
+  <si>
+    <t>Samurai</t>
+  </si>
+  <si>
+    <t>Scribe</t>
+  </si>
+  <si>
+    <t>European Explorer</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Sword Maker</t>
+  </si>
+  <si>
+    <t>Christian Missionary</t>
+  </si>
+  <si>
+    <t>Philosopher</t>
+  </si>
+  <si>
+    <t>Medusa</t>
+  </si>
+  <si>
+    <t>Zeus</t>
+  </si>
+  <si>
+    <t>Persian Invader</t>
+  </si>
+  <si>
+    <t>Olive Farmer</t>
+  </si>
+  <si>
+    <t>Spartan Soldier</t>
+  </si>
+  <si>
+    <t>Minotaur</t>
+  </si>
+  <si>
+    <t>Charioteer</t>
+  </si>
+  <si>
+    <t>Star Actor</t>
+  </si>
+  <si>
+    <t>Understudy</t>
+  </si>
+  <si>
+    <t>Musician</t>
+  </si>
+  <si>
+    <t>Choreographer</t>
+  </si>
+  <si>
+    <t>Playwrite</t>
+  </si>
+  <si>
+    <t>Critic</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Stagehand</t>
+  </si>
+  <si>
+    <t>Nobel Laureate</t>
+  </si>
+  <si>
+    <t>Philosophy Student</t>
+  </si>
+  <si>
+    <t>Groundskeeper</t>
+  </si>
+  <si>
+    <t>Bailiff</t>
+  </si>
+  <si>
+    <t>Sternographer</t>
+  </si>
+  <si>
+    <t>Defendant</t>
+  </si>
+  <si>
+    <t>Plaintiff</t>
+  </si>
+  <si>
+    <t>Video Camera Operator</t>
+  </si>
+  <si>
+    <t>Field Reporter</t>
+  </si>
+  <si>
+    <t>Anesthesiologist</t>
+  </si>
+  <si>
+    <t>Medical Student</t>
+  </si>
+  <si>
+    <t>Onlooker</t>
+  </si>
+  <si>
+    <t>Patient</t>
+  </si>
+  <si>
+    <t>Technician</t>
+  </si>
+  <si>
+    <t>Surgeon</t>
+  </si>
+  <si>
+    <t>Surgical Assistant</t>
+  </si>
+  <si>
+    <t>Mob boss</t>
+  </si>
+  <si>
+    <t>Hooligan</t>
+  </si>
+  <si>
+    <t>Distiller</t>
+  </si>
+  <si>
+    <t>Dancer</t>
+  </si>
+  <si>
+    <t>Cattle Wrangler</t>
+  </si>
+  <si>
+    <t>Grave Digger</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Grave Robber</t>
+  </si>
+  <si>
+    <t>Visitor</t>
+  </si>
+  <si>
+    <t>Mourner</t>
+  </si>
+  <si>
+    <t>Dr. Frankenstein</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -96,8 +640,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,27 +977,602 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C30512-2CBD-43D7-B2C6-490239A5FF95}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>6</v>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07E9DB3-389B-4132-8AC3-6E904449A4E7}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62265CB9-A5BC-412C-B2B8-65BACF40D809}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B294B56D-A6F7-4525-9853-F74EA5A9CBE1}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40CA2B50-31BF-4DEE-90AE-C521E716028D}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A265C3-3E77-4CC9-908D-9E8C20AC14E0}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C68B1C-477D-47B0-B67B-A5673C5BA619}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F56641-8E1A-4A9D-9A81-28C016C1ED6A}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E81B7DA-5AFF-4BE0-9CEC-BFA835BD9A84}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB76008-0799-45D7-88AB-DD8771ADD5E2}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F2C8305-6A95-4CB7-B8D3-DA65A7216392}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -462,27 +1582,712 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9841D522-56C4-4367-88B5-1E44452857C1}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8905608-5161-4764-8139-F83947D6D392}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9016141-F614-4E77-B66F-691B394CB448}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1FFAE60-39C4-4F4F-B5AA-22BC8747636C}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40319D8A-71D2-421B-A7EF-A73AC977610B}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C5BBC5E-25F8-4B3A-B714-B826DD479F30}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152B7EBD-CB0B-4732-8719-54796AD485F7}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D60F82-C027-4696-BD8D-8B4070A74C75}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE3CFFD-ACF3-4D84-A0EE-9BCB0B72816B}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68AF1CE-F921-46E3-8D14-5ADA99FF1469}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12BF9B7-6568-4AB7-A955-0089F46CB2D1}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D0FC0B-F3C8-4A40-BDA9-1E768F1733CC}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5881839C-BDD1-45E7-8531-6C6A00457ED5}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
